--- a/output/pdf_financials_xlsx/BOS.xlsx
+++ b/output/pdf_financials_xlsx/BOS.xlsx
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-40.412</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-31.892</v>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-31.892</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>28.304848</v>
+        <v>-28.304848</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>27.027119</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-40.412</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>67.584</v>
+        <v>-25.822</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-18.507</v>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>11.51624413401538</v>
+        <v>-4.400042258945095</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>-3.878613867611154</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-21.0828466792042</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>7.958143196480238</v>
+        <v>-7.958143196480238</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>-6.683781999559891</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-31.892</v>
@@ -29341,7 +29341,7 @@
         </is>
       </c>
       <c r="Q216" s="5" t="n">
-        <v>46.703</v>
+        <v>-46.703</v>
       </c>
       <c r="R216" s="5" t="n">
         <v>-31.892</v>

--- a/output/pdf_financials_xlsx/BOS.xlsx
+++ b/output/pdf_financials_xlsx/BOS.xlsx
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.69</v>
@@ -2448,7 +2448,7 @@
         <v>6.491</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>7.993</v>
       </c>
     </row>
     <row r="35">
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.69</v>
@@ -2564,7 +2564,7 @@
         <v>6.491</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>7.993</v>
       </c>
     </row>
     <row r="37">
@@ -3215,7 +3215,7 @@
         <v>0.637</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.623</v>
+        <v>0.748</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>2.067</v>
@@ -3260,7 +3260,7 @@
         <v>78.34</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>78.639</v>
+        <v>70.646</v>
       </c>
     </row>
     <row r="49">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -57334,7 +57334,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -58764,7 +58764,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E517" s="5" t="n">

--- a/output/pdf_financials_xlsx/BOS.xlsx
+++ b/output/pdf_financials_xlsx/BOS.xlsx
@@ -2077,49 +2077,49 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.565</v>
+        <v>0.28</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4.672</v>
+        <v>0.341</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5.667</v>
+        <v>0.383</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>6.556</v>
+        <v>0.74</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.605</v>
+        <v>2.165</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>9.58</v>
+        <v>2.827</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>10.385</v>
+        <v>3.409</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.684</v>
+        <v>3.305</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>10.966</v>
+        <v>3.119</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>13.35</v>
+        <v>2.935</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>20.881</v>
+        <v>7.746</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>21.905</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>22.345</v>
+        <v>9.218</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>21.012</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>19.523</v>
+        <v>7.166</v>
       </c>
     </row>
     <row r="29">
@@ -2135,22 +2135,22 @@
         <v>8.994999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>24.697</v>
+        <v>20.412</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.316</v>
+        <v>6.985</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10.507</v>
+        <v>5.223</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.426</v>
+        <v>4.61</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>18.011</v>
+        <v>11.571</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>18.129</v>
+        <v>11.376</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-25.822</v>
+        <v>-38.957</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-18.507</v>
+        <v>-31.116</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-16.41</v>
+        <v>-29.537</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.3</v>
+        <v>-10.512</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>15.334</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="30">
@@ -2201,22 +2201,22 @@
         <v>4.284945288942031</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10.48923130502737</v>
+        <v>8.66931973106931</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.005380150077871</v>
+        <v>2.472391335126717</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.224802772840955</v>
+        <v>2.100137516184288</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.411721146725907</v>
+        <v>1.9507034803766</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>5.941263594710227</v>
+        <v>3.81690972485659</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>5.945708391684076</v>
+        <v>3.730949234033761</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-4.400042258945095</v>
+        <v>-6.638232758180003</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-3.878613867611154</v>
+        <v>-6.521151407823454</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-3.851886626371691</v>
+        <v>-6.933161199460125</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.5942783910041755</v>
+        <v>-2.716110628798214</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>3.738149160293806</v>
+        <v>0.7257382320460846</v>
       </c>
     </row>
     <row r="31">
@@ -6259,49 +6259,49 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.165</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.827</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.409</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>3.305</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>3.119</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>2.935</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>7.746</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>9.218</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>7.166</v>
       </c>
     </row>
     <row r="101">
@@ -25603,7 +25603,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -31302,7 +31302,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -33543,7 +33543,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">

--- a/output/pdf_financials_xlsx/BOS.xlsx
+++ b/output/pdf_financials_xlsx/BOS.xlsx
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-46.703</v>
+        <v>-54.532</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-40.412</v>
@@ -1363,10 +1363,10 @@
         <v>4.316</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>7.829</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.52</v>
+        <v>-8.52</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>2.994</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-46.703</v>
+        <v>-54.532</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-40.412</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-38.957</v>
+        <v>-46.786</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-31.116</v>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-6.638232758180003</v>
+        <v>-7.97228631116897</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>-6.521151407823454</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.35670798797037</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-21.0828466792042</v>
@@ -6659,40 +6659,40 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>1.222</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>3.032</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>1.607</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.897</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.668</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="N107" s="3" t="n">
         <v>0</v>
@@ -6701,13 +6701,13 @@
         <v>0</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>1.241</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="108">
@@ -7187,49 +7187,49 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.311</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.449</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.714</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.504</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.199</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.581</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-1.754</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.971</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-2.22</v>
       </c>
       <c r="N116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-1.392</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-1.249</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.899</v>
       </c>
     </row>
     <row r="117">
@@ -7498,10 +7498,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.319</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>0</v>
@@ -26084,7 +26084,11 @@
           <t>Share-based payment expense 13, 14</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -27571,7 +27575,11 @@
           <t>Acquisition of intangible assets 8</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -33929,7 +33937,11 @@
           <t>Share-based payment expense 11,12</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -34218,7 +34230,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -34592,7 +34608,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -34881,7 +34901,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -35948,7 +35972,11 @@
           <t>Share-based payment expense 13</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -38013,7 +38041,11 @@
           <t>Deferred income tax expense 15</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -39692,7 +39724,11 @@
           <t>Equity-settled share-based payment expense 12</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -39892,7 +39928,11 @@
           <t>Deferred income tax expense 14</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -40898,7 +40938,11 @@
           <t>Equity-settled share-based payment expense 11</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -41292,7 +41336,11 @@
           <t>Deferred income tax expense 13</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -42793,7 +42841,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E354" s="5" t="n">
         <v>-1.683</v>
       </c>
@@ -42987,7 +43039,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E356" s="5" t="n">
         <v>0.42</v>
       </c>
@@ -45678,7 +45734,11 @@
           <t>Stock option expense - - 819</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -46181,7 +46241,11 @@
           <t>Stock option expense - - 382</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -46383,11 +46447,7 @@
           <t>Net income (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" s="5" t="n">
         <v>-1.308</v>
       </c>
@@ -48401,7 +48461,11 @@
           <t>Stock option expense - - 382</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E410" s="5" t="n">
         <v>0.382</v>
       </c>
@@ -49302,7 +49366,11 @@
           <t>Stock option expense - - 420 -</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E419" s="5" t="n">
         <v>0.42</v>
       </c>
@@ -51500,7 +51568,11 @@
           <t>Income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -51983,7 +52055,11 @@
           <t>Income tax recovery (expense) 17</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
